--- a/US/April CMA/US April CMA Data.xlsx
+++ b/US/April CMA/US April CMA Data.xlsx
@@ -19674,7 +19674,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.6640625" customWidth="1" min="1" max="2"/>
@@ -19746,37 +19746,42 @@
           <t>Task Model</t>
         </is>
       </c>
-      <c r="L1" s="32" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="M1" s="30" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>Need OI?</t>
         </is>
       </c>
-      <c r="N1" s="30" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>Point Biserial</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
@@ -19830,36 +19835,41 @@
           <t>1. Best Use</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>A. Gathering, Interpreting, and Using Evidence</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>11.06a.4</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N2" s="12">
+      <c r="O2" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 1]),"")</f>
         <v/>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>oppose independence movements in Latin America</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>remain neutral in the affairs of Latin America</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>become the protector of the Western Hemisphere</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>annex the countries of the Western Hemisphere</t>
         </is>
@@ -19913,36 +19923,41 @@
           <t>14. Stakeholder Issue</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>C. Comparison and Contextualization</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>11.05b.5</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N3" s="12">
+      <c r="O3" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 2]),"")</f>
         <v/>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>political equality</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>equal pay for equal work</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>improvements in living conditions</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>better job opportunities</t>
         </is>
@@ -19996,36 +20011,41 @@
           <t>9. Impact of Setting</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>C. Comparison and Contextualization</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>11.06b.1</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N4" s="12">
+      <c r="O4" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 3]),"")</f>
         <v/>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>The Senate had already repealed the Prohibition amendment.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>The country was dealing with public outrage over government corruption.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>President Wilson did not include women's demands in his Fourteen Points.</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Suffragists were picketing while German submarines were attacking American ships.</t>
         </is>
@@ -20079,36 +20099,41 @@
           <t>9. Impact of Setting</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>B. Chronological Reasoning and Causation</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>11.06c.2</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N5" s="12">
+      <c r="O5" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 6]),"")</f>
         <v/>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Foreign food imports replaced domestic production of crops.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Northern states banned all forms of racial discrimination.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Abolitionists promised a means of escape from slavery.</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Industrialization provided more employment opportunities.</t>
         </is>
@@ -20162,36 +20187,41 @@
           <t>8. Effect</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B. Chronological Reasoning and Causation</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>11.07b.1</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N6" s="12">
+      <c r="O6" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 8]),"")</f>
         <v/>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>The South became the new destination for most European immigrants.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>The Democratic Party declined in the northern half of the country.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>American culture was enriched by new forms of music and literature.</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Segregated communities throughout the nation came to an end.</t>
         </is>
@@ -20245,36 +20275,41 @@
           <t>9. Impact of Setting</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>C. Comparison and Contextualization</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>11.06c.3</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N7" s="12">
+      <c r="O7" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 4]),"")</f>
         <v/>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>responding to strikes by organized labor</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>implementing a new immigration system</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>involved in fighting a world war</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>concerned about a revolution in Russia</t>
         </is>
@@ -20328,36 +20363,41 @@
           <t>8. Effect</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>B. Chronological Reasoning and Causation</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>11.06c.3</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N8" s="12">
+      <c r="O8" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 5]),"")</f>
         <v/>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>freedom of expression</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>right to bear arms</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>right to counsel</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>trial by jury</t>
         </is>
@@ -20411,36 +20451,41 @@
           <t>18. Response to Problem</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>B. Chronological Reasoning and Causation</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>11.07c.5</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N9" s="12">
+      <c r="O9" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 8]),"")</f>
         <v/>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Fourteen Points</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>New Deal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Manifest Destiny</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Great Society</t>
         </is>
@@ -20495,36 +20540,41 @@
           <t>17. Problem</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>A. Gathering, Interpreting, and Using Evidence</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>11.07c.2</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N10" s="12">
+      <c r="O10" s="12">
         <f>IFERROR(PEARSON(Scores[MC Score],Scores[Question 9]),"")</f>
         <v/>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>the failure of Prohibition</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>the economic problems caused by the Great Depression</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>the destruction caused by the attack on Pearl Harbor</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>the possibility of a military alliance with Great Britain</t>
         </is>
